--- a/artfynd/A 55509-2025 artfynd.xlsx
+++ b/artfynd/A 55509-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59822783</v>
+        <v>76214238</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djuptjärnberget, Ly lm</t>
+          <t>Djupmyrberget utökn Ö, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662404.9727996003</v>
+        <v>662078</v>
       </c>
       <c r="R2" t="n">
-        <v>7176196.801477587</v>
+        <v>7176129</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59822779</v>
+        <v>59822778</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662488.0728767676</v>
+        <v>662500</v>
       </c>
       <c r="R3" t="n">
-        <v>7176281.07031028</v>
+        <v>7176322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2016-05-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59822778</v>
+        <v>76214613</v>
       </c>
       <c r="B4" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djuptjärnberget, Ly lm</t>
+          <t>Djupmyrberget utökn Ö, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662500.0444710555</v>
+        <v>662493</v>
       </c>
       <c r="R4" t="n">
-        <v>7176322.042795187</v>
+        <v>7176431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59822781</v>
+        <v>76214614</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djuptjärnberget, Ly lm</t>
+          <t>Djupmyrberget utökn Ö, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662436.0508832933</v>
+        <v>662194</v>
       </c>
       <c r="R5" t="n">
-        <v>7176249.956709116</v>
+        <v>7176254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59822780</v>
+        <v>59822776</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662467.019503234</v>
+        <v>662520</v>
       </c>
       <c r="R6" t="n">
-        <v>7176257.199372576</v>
+        <v>7176327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2016-05-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>59822776</v>
+        <v>59822779</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662519.9681326642</v>
+        <v>662488</v>
       </c>
       <c r="R7" t="n">
-        <v>7176326.975756349</v>
+        <v>7176281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2016-05-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59822782</v>
+        <v>59822780</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662413.1858482616</v>
+        <v>662467</v>
       </c>
       <c r="R8" t="n">
-        <v>7176211.830328444</v>
+        <v>7176257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2016-05-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-05-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>76214614</v>
+        <v>59822782</v>
       </c>
       <c r="B9" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupmyrberget utökn Ö, Ly lm</t>
+          <t>Djuptjärnberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662193.9850425008</v>
+        <v>662413</v>
       </c>
       <c r="R9" t="n">
-        <v>7176254.11266004</v>
+        <v>7176212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,62 +1439,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll, Per Nihlén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76214613</v>
+        <v>59822783</v>
       </c>
       <c r="B10" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupmyrberget utökn Ö, Ly lm</t>
+          <t>Djuptjärnberget, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662492.892042887</v>
+        <v>662405</v>
       </c>
       <c r="R10" t="n">
-        <v>7176431.057373764</v>
+        <v>7176197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll, Per Nihlén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76214238</v>
+        <v>59822785</v>
       </c>
       <c r="B11" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupmyrberget utökn Ö, Ly lm</t>
+          <t>Djuptjärnberget, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662077.8414681094</v>
+        <v>662095</v>
       </c>
       <c r="R11" t="n">
-        <v>7176129.036537469</v>
+        <v>7176182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-05-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll, Per Nihlén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 55509-2025 artfynd.xlsx
+++ b/artfynd/A 55509-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822778</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822776</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822779</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822780</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822782</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822783</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59822785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>